--- a/stakeholder_analysis/Communication_Plan.xlsx
+++ b/stakeholder_analysis/Communication_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaibh\Downloads\DLOS\stakeholder_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564078EA-AA92-4D35-B0BB-B6E17457ED9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC557B9F-917F-4A9F-8E2E-33A9DC3CAB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{05D0E8FC-BAC1-4408-9037-BA8EA225F85B}"/>
   </bookViews>
@@ -241,12 +241,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -255,16 +270,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
